--- a/private/planilla-alquileres-2026.xlsx
+++ b/private/planilla-alquileres-2026.xlsx
@@ -358,7 +358,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 2026-09-28 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 2026-10-07 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -928,19 +928,19 @@
     <t>Link</t>
   </si>
   <si>
-    <t>INDEC — IPC Nacional, nivel general (API oficial de series de tiempo)</t>
+    <t>INDEC: IPC Nacional, nivel general (API oficial de series de tiempo)</t>
   </si>
   <si>
     <t>https://datos.gob.ar/series/api/series/?ids=148.3_INIVELNAL_DICI_M_26&amp;format=json</t>
   </si>
   <si>
-    <t>INDEC — Índice de precios al consumidor (informes técnicos mensuales)</t>
+    <t>INDEC: Índice de precios al consumidor (informes técnicos mensuales)</t>
   </si>
   <si>
     <t>https://www.indec.gob.ar/indec/web/Nivel4-Tema-3-5-31</t>
   </si>
   <si>
-    <t>DNU 70/2023 — arts. 249 y 257 (alquileres: libre pacto del índice de ajuste)</t>
+    <t>DNU 70/2023: arts. 249 y 257 (alquileres: libre pacto del índice de ajuste)</t>
   </si>
   <si>
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/395000-399999/395521/norma.htm</t>
@@ -952,7 +952,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/235000-239999/235975/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-09-28. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-07. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>

--- a/private/planilla-alquileres-2026.xlsx
+++ b/private/planilla-alquileres-2026.xlsx
@@ -358,7 +358,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 2026-10-07 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 2026-10-15 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -952,7 +952,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/235000-239999/235975/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-07. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-15. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>

--- a/private/planilla-alquileres-2026.xlsx
+++ b/private/planilla-alquileres-2026.xlsx
@@ -358,7 +358,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 2026-10-15 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 2026-10-23 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -952,7 +952,7 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/235000-239999/235975/texact.htm</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-15. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-23. Cada vez que el INDEC publica un IPC nuevo regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
